--- a/payment_forms/028_custom_cufflink_order_form--payment_forms.xlsx
+++ b/payment_forms/028_custom_cufflink_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_1':_none}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_1': None}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_2':_none}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_2': None}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>silver_cufflink</t>
+          <t>silver cufflink</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gold_cufflink</t>
+          <t>gold cufflink</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>small_cufflink</t>
+          <t>small cufflink</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medium_cufflink</t>
+          <t>medium cufflink</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>large_cufflink</t>
+          <t>large cufflink</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>blue_cufflink</t>
+          <t>blue cufflink</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>red_cufflink</t>
+          <t>red cufflink</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>green_cufflink</t>
+          <t>green cufflink</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>black_cufflink</t>
+          <t>black cufflink</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>white_cufflink</t>
+          <t>white cufflink</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>missouri</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>missouri</t>
+          <t>montana</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>montana</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>montana</t>
+          <t>nebraska</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nebraska</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nebraska</t>
+          <t>nevada</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nevada</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>nevada</t>
+          <t>new hampshire</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>new_hampshire</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>new_hampshire</t>
+          <t>new jersey</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>new_jersey</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>new_jersey</t>
+          <t>new mexico</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>new_mexico</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>new_mexico</t>
+          <t>new york</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>north carolina</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>north_carolina</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>north_carolina</t>
+          <t>north dakota</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>north_dakota</t>
+          <t>northern_marianas</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>north_dakota</t>
+          <t>northern marianas</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>northern_marianas</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>northern_marianas</t>
+          <t>oklahoma</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>oklahoma</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>oklahoma</t>
+          <t>oregon</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>oregon</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>oregon</t>
+          <t>pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pennsylvania</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pennsylvania</t>
+          <t>rhode island</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>rhode_island</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rhode_island</t>
+          <t>south carolina</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>south_carolina</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>south_carolina</t>
+          <t>south dakota</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>south_dakota</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>south_dakota</t>
+          <t>tennessee</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tennessee</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tennessee</t>
+          <t>texas</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>texas</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>texas</t>
+          <t>utah</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>utah</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>utah</t>
+          <t>vermont</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>vermont</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>vermont</t>
+          <t>virginia</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>virginia</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>virginia</t>
+          <t>washington</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>washington</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>washington</t>
+          <t>west virginia</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>west_virginia</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>west_virginia</t>
+          <t>wisconsin</t>
         </is>
       </c>
     </row>
@@ -1915,27 +1915,10 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wisconsin</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
-        <is>
-          <t>wisconsin</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>shipping_state_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>wyoming</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
         <is>
           <t>wyoming</t>
         </is>
